--- a/artfynd/A 32968-2021 artfynd.xlsx
+++ b/artfynd/A 32968-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32968-2021 artfynd.xlsx
+++ b/artfynd/A 32968-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100236034</v>
+        <v>100236042</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460308.1419610605</v>
+        <v>460304</v>
       </c>
       <c r="R2" t="n">
-        <v>7163566.64470496</v>
+        <v>7163025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100236033</v>
+        <v>100236043</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460282.8200018132</v>
+        <v>460329</v>
       </c>
       <c r="R3" t="n">
-        <v>7163603.485892154</v>
+        <v>7163037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100236052</v>
+        <v>100236044</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460348.4826405692</v>
+        <v>460335</v>
       </c>
       <c r="R4" t="n">
-        <v>7163461.309904078</v>
+        <v>7163051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100236020</v>
+        <v>100236045</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,38 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460332.3946061843</v>
+        <v>460297</v>
       </c>
       <c r="R5" t="n">
-        <v>7162921.101856125</v>
+        <v>7163077</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,24 +1034,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100236063</v>
+        <v>100236052</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460277.0288205367</v>
+        <v>460348</v>
       </c>
       <c r="R6" t="n">
-        <v>7162963.49874028</v>
+        <v>7163461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100236045</v>
+        <v>100236059</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460297.4348083354</v>
+        <v>460348</v>
       </c>
       <c r="R7" t="n">
-        <v>7163076.648804148</v>
+        <v>7163463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100236059</v>
+        <v>100236020</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,34 +1268,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460348.5106843009</v>
+        <v>460332</v>
       </c>
       <c r="R8" t="n">
-        <v>7163463.457272361</v>
+        <v>7162921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,22 +1326,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,15 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100236043</v>
+        <v>100236033</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,34 +1374,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460328.7486986966</v>
+        <v>460283</v>
       </c>
       <c r="R9" t="n">
-        <v>7163037.145572864</v>
+        <v>7163604</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,22 +1432,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100236044</v>
+        <v>100236034</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,34 +1480,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460334.5247138075</v>
+        <v>460308</v>
       </c>
       <c r="R10" t="n">
-        <v>7163051.247118079</v>
+        <v>7163567</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,22 +1538,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,15 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100236042</v>
+        <v>111251411</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,13 +1610,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460304.072069722</v>
+        <v>460376</v>
       </c>
       <c r="R11" t="n">
-        <v>7163025.009415426</v>
+        <v>7162890</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,19 +1643,14 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,27 +1665,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111251411</v>
+        <v>111251412</v>
       </c>
       <c r="B12" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460375.8651575765</v>
+        <v>460284</v>
       </c>
       <c r="R12" t="n">
-        <v>7162890.030951658</v>
+        <v>7163213</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1895,19 +1745,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
